--- a/product-definitions/spreadsheet/flux-components.xlsx
+++ b/product-definitions/spreadsheet/flux-components.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1602" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1602" uniqueCount="231">
   <si>
     <t>Name</t>
   </si>
@@ -161,15 +161,12 @@
     <t>Specific Humidity (Q)</t>
   </si>
   <si>
-    <t>water_vapur_partial_pressure_in_air</t>
+    <t>water_vapor_partial_pressure_in_air</t>
   </si>
   <si>
     <t>Pa</t>
   </si>
   <si>
-    <t>water_vapor_partial_pressure_in_air</t>
-  </si>
-  <si>
     <t>Water Vapor Partial Pressure in air</t>
   </si>
   <si>
@@ -215,25 +212,25 @@
     <t>eastward_wind_rotated_to_run</t>
   </si>
   <si>
-    <t>Eastward Wind Component (U rotated to run)</t>
+    <t>U Wind Component (U rotated to run)</t>
   </si>
   <si>
     <t>northward_wind_rotated_to_run</t>
   </si>
   <si>
-    <t>Northward Wind Component (V rotated to run)</t>
+    <t>V Wind Component (V rotated to run)</t>
   </si>
   <si>
     <t>upward_air_velocity_rotated_to_run</t>
   </si>
   <si>
-    <t>Upward Air Velocity Component (W rotated to run)</t>
+    <t>W Air Velocity Component (W rotated to run)</t>
   </si>
   <si>
     <t>skew_eastward_wind</t>
   </si>
   <si>
-    <t>Skew of Eastward Wind Component (U rotated to run)</t>
+    <t>Skew of U Wind Component (U rotated to run)</t>
   </si>
   <si>
     <t>time: skew</t>
@@ -242,13 +239,13 @@
     <t>skew_northward_wind</t>
   </si>
   <si>
-    <t>Skew of Northward Wind Component (V rotated to run)</t>
+    <t>Skew of V Wind Component (V rotated to run)</t>
   </si>
   <si>
     <t>skew_upward_air_velocity</t>
   </si>
   <si>
-    <t>Skew of Upward Air Velocity Component (W rotated to run)</t>
+    <t>Skew of W Air Velocity Component (W rotated to run)</t>
   </si>
   <si>
     <t>skew_sonic_air_temperature</t>
@@ -730,7 +727,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -756,14 +753,9 @@
     <font>
       <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <color theme="1"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -781,7 +773,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="15">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -805,30 +797,23 @@
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="top"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2162,7 +2147,7 @@
       <c r="B3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2178,7 +2163,7 @@
       <c r="B5" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2194,7 +2179,7 @@
       <c r="B7" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="8" t="s">
         <v>19</v>
       </c>
     </row>
@@ -2202,7 +2187,7 @@
       <c r="B8" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -2240,7 +2225,7 @@
       <c r="B14" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -2280,7 +2265,7 @@
       <c r="B19" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="10">
+      <c r="C19" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -2318,7 +2303,7 @@
       <c r="B25" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -2358,7 +2343,7 @@
       <c r="B30" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C30" s="10">
+      <c r="C30" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -2388,7 +2373,7 @@
     </row>
     <row r="34" ht="12.0" customHeight="1"/>
     <row r="35" ht="12.0" customHeight="1">
-      <c r="A35" s="9" t="s">
+      <c r="A35" s="8" t="s">
         <v>32</v>
       </c>
     </row>
@@ -2396,7 +2381,7 @@
       <c r="B36" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C36" s="9" t="s">
+      <c r="C36" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -2420,7 +2405,7 @@
       <c r="B39" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C39" s="9" t="s">
+      <c r="C39" s="8" t="s">
         <v>32</v>
       </c>
     </row>
@@ -2428,7 +2413,7 @@
       <c r="B40" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C40" s="9" t="s">
+      <c r="C40" s="8" t="s">
         <v>35</v>
       </c>
     </row>
@@ -2436,7 +2421,7 @@
       <c r="B41" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C41" s="10">
+      <c r="C41" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -2482,7 +2467,7 @@
       <c r="B48" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C48" s="9" t="s">
+      <c r="C48" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -2514,7 +2499,7 @@
       <c r="B52" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C52" s="9" t="s">
+      <c r="C52" s="8" t="s">
         <v>40</v>
       </c>
     </row>
@@ -2522,7 +2507,7 @@
       <c r="B53" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C53" s="10">
+      <c r="C53" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -2568,7 +2553,7 @@
       <c r="B60" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C60" s="9" t="s">
+      <c r="C60" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -2600,7 +2585,7 @@
       <c r="B64" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C64" s="9" t="s">
+      <c r="C64" s="8" t="s">
         <v>43</v>
       </c>
     </row>
@@ -2608,7 +2593,7 @@
       <c r="B65" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C65" s="10">
+      <c r="C65" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -2654,7 +2639,7 @@
       <c r="B72" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C72" s="9" t="s">
+      <c r="C72" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -2686,7 +2671,7 @@
       <c r="B76" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C76" s="9" t="s">
+      <c r="C76" s="8" t="s">
         <v>45</v>
       </c>
     </row>
@@ -2694,7 +2679,7 @@
       <c r="B77" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C77" s="10">
+      <c r="C77" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -2732,7 +2717,7 @@
     </row>
     <row r="82" ht="12.0" customHeight="1"/>
     <row r="83" ht="12.0" customHeight="1">
-      <c r="A83" s="9" t="s">
+      <c r="A83" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -2740,7 +2725,7 @@
       <c r="B84" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C84" s="9" t="s">
+      <c r="C84" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -2772,7 +2757,7 @@
       <c r="B88" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C88" s="9" t="s">
+      <c r="C88" s="8" t="s">
         <v>48</v>
       </c>
     </row>
@@ -2780,7 +2765,7 @@
       <c r="B89" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C89" s="10">
+      <c r="C89" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -2818,7 +2803,7 @@
     </row>
     <row r="94" ht="12.0" customHeight="1"/>
     <row r="95" ht="12.0" customHeight="1">
-      <c r="A95" s="9" t="s">
+      <c r="A95" s="10" t="s">
         <v>49</v>
       </c>
     </row>
@@ -2826,7 +2811,7 @@
       <c r="B96" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C96" s="9" t="s">
+      <c r="C96" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -2851,22 +2836,22 @@
         <v>17</v>
       </c>
       <c r="C99" s="8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="100" ht="12.0" customHeight="1">
       <c r="B100" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C100" s="9" t="s">
-        <v>52</v>
+      <c r="C100" s="8" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="101" ht="12.0" customHeight="1">
       <c r="B101" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C101" s="10">
+      <c r="C101" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -2904,15 +2889,15 @@
     </row>
     <row r="106" ht="12.0" customHeight="1"/>
     <row r="107" ht="12.0" customHeight="1">
-      <c r="A107" s="9" t="s">
-        <v>53</v>
+      <c r="A107" s="8" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="108" ht="12.0" customHeight="1">
       <c r="B108" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C108" s="9" t="s">
+      <c r="C108" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -2937,22 +2922,22 @@
         <v>17</v>
       </c>
       <c r="C111" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="112" ht="12.0" customHeight="1">
       <c r="B112" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C112" s="9" t="s">
-        <v>54</v>
+      <c r="C112" s="8" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="113" ht="12.0" customHeight="1">
       <c r="B113" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C113" s="10">
+      <c r="C113" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -2990,15 +2975,15 @@
     </row>
     <row r="118" ht="12.0" customHeight="1"/>
     <row r="119" ht="12.0" customHeight="1">
-      <c r="A119" s="9" t="s">
-        <v>55</v>
+      <c r="A119" s="8" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="120" ht="12.0" customHeight="1">
       <c r="B120" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C120" s="9" t="s">
+      <c r="C120" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -3028,14 +3013,14 @@
         <v>18</v>
       </c>
       <c r="C124" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="125" ht="12.0" customHeight="1">
       <c r="B125" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C125" s="10">
+      <c r="C125" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -3074,14 +3059,14 @@
     <row r="130" ht="12.0" customHeight="1"/>
     <row r="131" ht="12.0" customHeight="1">
       <c r="A131" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="132" ht="12.0" customHeight="1">
       <c r="B132" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C132" s="9" t="s">
+      <c r="C132" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -3110,15 +3095,15 @@
       <c r="B136" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C136" s="9" t="s">
-        <v>58</v>
+      <c r="C136" s="8" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="137" ht="12.0" customHeight="1">
       <c r="B137" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C137" s="10">
+      <c r="C137" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -3156,15 +3141,15 @@
     </row>
     <row r="142" ht="12.0" customHeight="1"/>
     <row r="143" ht="12.0" customHeight="1">
-      <c r="A143" s="9" t="s">
-        <v>59</v>
+      <c r="A143" s="8" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="144" ht="12.0" customHeight="1">
       <c r="B144" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C144" s="9" t="s">
+      <c r="C144" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -3181,7 +3166,7 @@
         <v>2</v>
       </c>
       <c r="C146" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="147" ht="12.0" customHeight="1">
@@ -3189,7 +3174,7 @@
         <v>17</v>
       </c>
       <c r="C147" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="148" ht="12.0" customHeight="1">
@@ -3197,14 +3182,14 @@
         <v>18</v>
       </c>
       <c r="C148" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="149" ht="12.0" customHeight="1">
       <c r="B149" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C149" s="10">
+      <c r="C149" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -3242,15 +3227,15 @@
     </row>
     <row r="154" ht="12.0" customHeight="1"/>
     <row r="155" ht="12.0" customHeight="1">
-      <c r="A155" s="9" t="s">
-        <v>62</v>
+      <c r="A155" s="8" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="156" ht="12.0" customHeight="1">
       <c r="B156" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C156" s="9" t="s">
+      <c r="C156" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -3267,30 +3252,30 @@
         <v>2</v>
       </c>
       <c r="C158" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="159" ht="12.0" customHeight="1">
       <c r="B159" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C159" s="9" t="s">
-        <v>62</v>
+      <c r="C159" s="8" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="160" ht="12.0" customHeight="1">
       <c r="B160" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C160" s="9" t="s">
-        <v>63</v>
+      <c r="C160" s="8" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="161" ht="12.0" customHeight="1">
       <c r="B161" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C161" s="10">
+      <c r="C161" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -3328,15 +3313,15 @@
     </row>
     <row r="166" ht="12.0" customHeight="1"/>
     <row r="167" ht="12.0" customHeight="1">
-      <c r="A167" s="9" t="s">
-        <v>64</v>
+      <c r="A167" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="168" ht="12.0" customHeight="1">
       <c r="B168" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C168" s="9" t="s">
+      <c r="C168" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -3353,7 +3338,7 @@
         <v>2</v>
       </c>
       <c r="C170" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="171" ht="12.0" customHeight="1">
@@ -3361,7 +3346,7 @@
         <v>17</v>
       </c>
       <c r="C171" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="172" ht="12.0" customHeight="1">
@@ -3369,14 +3354,14 @@
         <v>18</v>
       </c>
       <c r="C172" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="173" ht="12.0" customHeight="1">
       <c r="B173" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C173" s="10">
+      <c r="C173" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -3416,15 +3401,15 @@
       <c r="C178" s="4"/>
     </row>
     <row r="179" ht="12.0" customHeight="1">
-      <c r="A179" s="9" t="s">
-        <v>66</v>
+      <c r="A179" s="8" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="180" ht="12.0" customHeight="1">
       <c r="B180" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C180" s="9" t="s">
+      <c r="C180" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -3441,7 +3426,7 @@
         <v>2</v>
       </c>
       <c r="C182" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="183" ht="12.0" customHeight="1">
@@ -3453,15 +3438,15 @@
       <c r="B184" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C184" s="9" t="s">
-        <v>67</v>
+      <c r="C184" s="10" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="185" ht="12.0" customHeight="1">
       <c r="B185" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C185" s="10">
+      <c r="C185" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -3501,15 +3486,15 @@
       <c r="C190" s="4"/>
     </row>
     <row r="191" ht="12.0" customHeight="1">
-      <c r="A191" s="9" t="s">
-        <v>68</v>
+      <c r="A191" s="8" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="192" ht="12.0" customHeight="1">
       <c r="B192" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C192" s="9" t="s">
+      <c r="C192" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -3526,7 +3511,7 @@
         <v>2</v>
       </c>
       <c r="C194" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="195" ht="12.0" customHeight="1">
@@ -3538,15 +3523,15 @@
       <c r="B196" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C196" s="9" t="s">
-        <v>69</v>
+      <c r="C196" s="10" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="197" ht="12.0" customHeight="1">
       <c r="B197" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C197" s="10">
+      <c r="C197" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -3584,15 +3569,15 @@
     </row>
     <row r="202" ht="12.0" customHeight="1"/>
     <row r="203" ht="12.0" customHeight="1">
-      <c r="A203" s="9" t="s">
-        <v>70</v>
+      <c r="A203" s="8" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="204" ht="12.0" customHeight="1">
       <c r="B204" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C204" s="9" t="s">
+      <c r="C204" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -3609,7 +3594,7 @@
         <v>2</v>
       </c>
       <c r="C206" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="207" ht="12.0" customHeight="1">
@@ -3621,15 +3606,15 @@
       <c r="B208" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C208" s="9" t="s">
-        <v>71</v>
+      <c r="C208" s="10" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="209" ht="12.0" customHeight="1">
       <c r="B209" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C209" s="10">
+      <c r="C209" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -3667,15 +3652,15 @@
     </row>
     <row r="214" ht="12.0" customHeight="1"/>
     <row r="215" ht="12.0" customHeight="1">
-      <c r="A215" s="9" t="s">
-        <v>72</v>
+      <c r="A215" s="8" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="216" ht="12.0" customHeight="1">
       <c r="B216" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C216" s="9" t="s">
+      <c r="C216" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -3704,15 +3689,15 @@
       <c r="B220" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C220" s="9" t="s">
-        <v>73</v>
+      <c r="C220" s="10" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="221" ht="12.0" customHeight="1">
       <c r="B221" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C221" s="10">
+      <c r="C221" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -3736,8 +3721,8 @@
       <c r="B224" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C224" s="9" t="s">
-        <v>74</v>
+      <c r="C224" s="8" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="225" ht="12.0" customHeight="1">
@@ -3750,15 +3735,15 @@
     </row>
     <row r="226" ht="12.0" customHeight="1"/>
     <row r="227" ht="12.0" customHeight="1">
-      <c r="A227" s="9" t="s">
-        <v>75</v>
+      <c r="A227" s="8" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="228" ht="12.0" customHeight="1">
       <c r="B228" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C228" s="9" t="s">
+      <c r="C228" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -3787,15 +3772,15 @@
       <c r="B232" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C232" s="9" t="s">
-        <v>76</v>
+      <c r="C232" s="10" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="233" ht="12.0" customHeight="1">
       <c r="B233" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C233" s="10">
+      <c r="C233" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -3819,8 +3804,8 @@
       <c r="B236" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C236" s="9" t="s">
-        <v>74</v>
+      <c r="C236" s="8" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="237" ht="12.0" customHeight="1">
@@ -3833,15 +3818,15 @@
     </row>
     <row r="238" ht="12.0" customHeight="1"/>
     <row r="239" ht="12.0" customHeight="1">
-      <c r="A239" s="9" t="s">
-        <v>77</v>
+      <c r="A239" s="8" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="240" ht="12.0" customHeight="1">
       <c r="B240" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C240" s="9" t="s">
+      <c r="C240" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -3870,15 +3855,15 @@
       <c r="B244" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C244" s="9" t="s">
-        <v>78</v>
+      <c r="C244" s="10" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="245" ht="12.0" customHeight="1">
       <c r="B245" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C245" s="10">
+      <c r="C245" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -3902,8 +3887,8 @@
       <c r="B248" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C248" s="9" t="s">
-        <v>74</v>
+      <c r="C248" s="8" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="249" ht="12.0" customHeight="1">
@@ -3916,15 +3901,15 @@
     </row>
     <row r="250" ht="12.0" customHeight="1"/>
     <row r="251" ht="12.0" customHeight="1">
-      <c r="A251" s="9" t="s">
-        <v>79</v>
+      <c r="A251" s="8" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="252" ht="12.0" customHeight="1">
       <c r="B252" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C252" s="9" t="s">
+      <c r="C252" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -3953,15 +3938,15 @@
       <c r="B256" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C256" s="12" t="s">
-        <v>80</v>
+      <c r="C256" s="8" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="257" ht="12.0" customHeight="1">
       <c r="B257" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C257" s="10">
+      <c r="C257" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -3985,8 +3970,8 @@
       <c r="B260" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C260" s="9" t="s">
-        <v>74</v>
+      <c r="C260" s="8" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="261" ht="12.0" customHeight="1">
@@ -3999,15 +3984,15 @@
     </row>
     <row r="262" ht="12.0" customHeight="1"/>
     <row r="263" ht="12.0" customHeight="1">
-      <c r="A263" s="9" t="s">
-        <v>81</v>
+      <c r="A263" s="8" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="264" ht="12.0" customHeight="1">
       <c r="B264" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C264" s="9" t="s">
+      <c r="C264" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -4036,15 +4021,15 @@
       <c r="B268" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C268" s="9" t="s">
-        <v>82</v>
+      <c r="C268" s="8" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="269" ht="12.0" customHeight="1">
       <c r="B269" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C269" s="10">
+      <c r="C269" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -4068,8 +4053,8 @@
       <c r="B272" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C272" s="9" t="s">
-        <v>83</v>
+      <c r="C272" s="8" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="273" ht="12.0" customHeight="1">
@@ -4082,15 +4067,15 @@
     </row>
     <row r="274" ht="12.0" customHeight="1"/>
     <row r="275" ht="12.0" customHeight="1">
-      <c r="A275" s="9" t="s">
-        <v>84</v>
+      <c r="A275" s="8" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="276" ht="12.0" customHeight="1">
       <c r="B276" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C276" s="9" t="s">
+      <c r="C276" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -4119,15 +4104,15 @@
       <c r="B280" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C280" s="9" t="s">
-        <v>85</v>
+      <c r="C280" s="8" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="281" ht="12.0" customHeight="1">
       <c r="B281" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C281" s="10">
+      <c r="C281" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -4151,8 +4136,8 @@
       <c r="B284" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C284" s="9" t="s">
-        <v>83</v>
+      <c r="C284" s="8" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="285" ht="12.0" customHeight="1">
@@ -4165,15 +4150,15 @@
     </row>
     <row r="286" ht="12.0" customHeight="1"/>
     <row r="287" ht="12.0" customHeight="1">
-      <c r="A287" s="9" t="s">
-        <v>86</v>
+      <c r="A287" s="8" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="288" ht="12.0" customHeight="1">
       <c r="B288" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C288" s="9" t="s">
+      <c r="C288" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -4202,15 +4187,15 @@
       <c r="B292" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C292" s="9" t="s">
-        <v>87</v>
+      <c r="C292" s="8" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="293" ht="12.0" customHeight="1">
       <c r="B293" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C293" s="10">
+      <c r="C293" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -4234,8 +4219,8 @@
       <c r="B296" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C296" s="9" t="s">
-        <v>83</v>
+      <c r="C296" s="8" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="297" ht="12.0" customHeight="1">
@@ -4248,15 +4233,15 @@
     </row>
     <row r="298" ht="12.0" customHeight="1"/>
     <row r="299" ht="12.0" customHeight="1">
-      <c r="A299" s="9" t="s">
-        <v>88</v>
+      <c r="A299" s="8" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="300" ht="12.0" customHeight="1">
       <c r="B300" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C300" s="9" t="s">
+      <c r="C300" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -4285,15 +4270,15 @@
       <c r="B304" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C304" s="9" t="s">
-        <v>89</v>
+      <c r="C304" s="8" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="305" ht="12.0" customHeight="1">
       <c r="B305" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C305" s="10">
+      <c r="C305" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -4317,8 +4302,8 @@
       <c r="B308" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C308" s="9" t="s">
-        <v>83</v>
+      <c r="C308" s="8" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="309" ht="12.0" customHeight="1">
@@ -4332,14 +4317,14 @@
     <row r="310" ht="12.0" customHeight="1"/>
     <row r="311" ht="12.0" customHeight="1">
       <c r="A311" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="312" ht="12.0" customHeight="1">
       <c r="B312" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C312" s="9" t="s">
+      <c r="C312" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -4369,14 +4354,14 @@
         <v>18</v>
       </c>
       <c r="C316" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="317" ht="12.0" customHeight="1">
       <c r="B317" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C317" s="10">
+      <c r="C317" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -4415,14 +4400,14 @@
     <row r="322" ht="12.0" customHeight="1"/>
     <row r="323" ht="12.0" customHeight="1">
       <c r="A323" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="324" ht="12.0" customHeight="1">
       <c r="B324" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C324" s="9" t="s">
+      <c r="C324" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -4452,14 +4437,14 @@
         <v>18</v>
       </c>
       <c r="C328" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="329" ht="12.0" customHeight="1">
       <c r="B329" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C329" s="10">
+      <c r="C329" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -4498,14 +4483,14 @@
     <row r="334" ht="12.0" customHeight="1"/>
     <row r="335" ht="12.0" customHeight="1">
       <c r="A335" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="336" ht="12.0" customHeight="1">
       <c r="B336" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C336" s="9" t="s">
+      <c r="C336" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -4535,14 +4520,14 @@
         <v>18</v>
       </c>
       <c r="C340" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="341" ht="12.0" customHeight="1">
       <c r="B341" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C341" s="10">
+      <c r="C341" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -4581,14 +4566,14 @@
     <row r="346" ht="12.0" customHeight="1"/>
     <row r="347" ht="12.0" customHeight="1">
       <c r="A347" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="348" ht="12.0" customHeight="1">
       <c r="B348" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C348" s="9" t="s">
+      <c r="C348" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -4605,7 +4590,7 @@
         <v>2</v>
       </c>
       <c r="C350" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="351" ht="12.0" customHeight="1">
@@ -4617,15 +4602,15 @@
       <c r="B352" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C352" s="9" t="s">
-        <v>97</v>
+      <c r="C352" s="8" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="353" ht="12.0" customHeight="1">
       <c r="B353" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C353" s="10">
+      <c r="C353" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -4664,14 +4649,14 @@
     <row r="358" ht="12.0" customHeight="1"/>
     <row r="359" ht="12.0" customHeight="1">
       <c r="A359" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="360" ht="12.0" customHeight="1">
       <c r="B360" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C360" s="9" t="s">
+      <c r="C360" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -4688,7 +4673,7 @@
         <v>2</v>
       </c>
       <c r="C362" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="363" ht="12.0" customHeight="1">
@@ -4700,15 +4685,15 @@
       <c r="B364" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C364" s="9" t="s">
-        <v>100</v>
+      <c r="C364" s="8" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="365" ht="12.0" customHeight="1">
       <c r="B365" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C365" s="10">
+      <c r="C365" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -4747,14 +4732,14 @@
     <row r="370" ht="12.0" customHeight="1"/>
     <row r="371" ht="12.0" customHeight="1">
       <c r="A371" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="372" ht="12.0" customHeight="1">
       <c r="B372" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C372" s="9" t="s">
+      <c r="C372" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -4783,15 +4768,15 @@
       <c r="B376" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C376" s="9" t="s">
-        <v>102</v>
+      <c r="C376" s="8" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="377" ht="12.0" customHeight="1">
       <c r="B377" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C377" s="10">
+      <c r="C377" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -4829,15 +4814,15 @@
     </row>
     <row r="382" ht="12.0" customHeight="1"/>
     <row r="383" ht="12.0" customHeight="1">
-      <c r="A383" s="9" t="s">
-        <v>103</v>
+      <c r="A383" s="8" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="384" ht="12.0" customHeight="1">
       <c r="B384" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C384" s="9" t="s">
+      <c r="C384" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -4854,7 +4839,7 @@
         <v>2</v>
       </c>
       <c r="C386" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="387" ht="12.0" customHeight="1">
@@ -4866,15 +4851,15 @@
       <c r="B388" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C388" s="9" t="s">
-        <v>104</v>
+      <c r="C388" s="8" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="389" ht="12.0" customHeight="1">
       <c r="B389" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C389" s="10">
+      <c r="C389" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -4899,7 +4884,7 @@
         <v>36</v>
       </c>
       <c r="C392" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="393" ht="12.0" customHeight="1">
@@ -4912,15 +4897,15 @@
     </row>
     <row r="394" ht="12.0" customHeight="1"/>
     <row r="395" ht="12.0" customHeight="1">
-      <c r="A395" s="9" t="s">
-        <v>106</v>
+      <c r="A395" s="8" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="396" ht="12.0" customHeight="1">
       <c r="B396" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C396" s="9" t="s">
+      <c r="C396" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -4949,15 +4934,15 @@
       <c r="B400" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C400" s="9" t="s">
-        <v>107</v>
+      <c r="C400" s="8" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="401" ht="12.0" customHeight="1">
       <c r="B401" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C401" s="10">
+      <c r="C401" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -4996,14 +4981,14 @@
     <row r="406" ht="12.0" customHeight="1"/>
     <row r="407" ht="12.0" customHeight="1">
       <c r="A407" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="408" ht="12.0" customHeight="1">
       <c r="B408" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C408" s="9" t="s">
+      <c r="C408" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -5020,7 +5005,7 @@
         <v>2</v>
       </c>
       <c r="C410" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="411" ht="12.0" customHeight="1">
@@ -5033,14 +5018,14 @@
         <v>18</v>
       </c>
       <c r="C412" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="413" ht="12.0" customHeight="1">
       <c r="B413" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C413" s="10">
+      <c r="C413" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -5065,7 +5050,7 @@
         <v>36</v>
       </c>
       <c r="C416" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="417" ht="12.0" customHeight="1">
@@ -5079,14 +5064,14 @@
     <row r="418" ht="12.0" customHeight="1"/>
     <row r="419" ht="12.0" customHeight="1">
       <c r="A419" s="8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="420" ht="12.0" customHeight="1">
       <c r="B420" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C420" s="9" t="s">
+      <c r="C420" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -5103,7 +5088,7 @@
         <v>2</v>
       </c>
       <c r="C422" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="423" ht="12.0" customHeight="1">
@@ -5116,14 +5101,14 @@
         <v>18</v>
       </c>
       <c r="C424" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="425" ht="12.0" customHeight="1">
       <c r="B425" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C425" s="10">
+      <c r="C425" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -5148,7 +5133,7 @@
         <v>36</v>
       </c>
       <c r="C428" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="429" ht="12.0" customHeight="1">
@@ -5162,14 +5147,14 @@
     <row r="430" ht="12.0" customHeight="1"/>
     <row r="431" ht="12.0" customHeight="1">
       <c r="A431" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="432" ht="12.0" customHeight="1">
       <c r="B432" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C432" s="9" t="s">
+      <c r="C432" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -5186,7 +5171,7 @@
         <v>2</v>
       </c>
       <c r="C434" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="435" ht="12.0" customHeight="1">
@@ -5199,14 +5184,14 @@
         <v>18</v>
       </c>
       <c r="C436" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="437" ht="12.0" customHeight="1">
       <c r="B437" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C437" s="10">
+      <c r="C437" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -5231,7 +5216,7 @@
         <v>36</v>
       </c>
       <c r="C440" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="441" ht="12.0" customHeight="1">
@@ -5245,14 +5230,14 @@
     <row r="442" ht="12.0" customHeight="1"/>
     <row r="443" ht="12.0" customHeight="1">
       <c r="A443" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="444" ht="12.0" customHeight="1">
       <c r="B444" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C444" s="9" t="s">
+      <c r="C444" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -5282,14 +5267,14 @@
         <v>18</v>
       </c>
       <c r="C448" s="8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="449" ht="12.0" customHeight="1">
       <c r="B449" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C449" s="10">
+      <c r="C449" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -5314,7 +5299,7 @@
         <v>36</v>
       </c>
       <c r="C452" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="453" ht="12.0" customHeight="1">
@@ -5328,14 +5313,14 @@
     <row r="454" ht="12.0" customHeight="1"/>
     <row r="455" ht="12.0" customHeight="1">
       <c r="A455" s="8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="456" ht="12.0" customHeight="1">
       <c r="B456" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C456" s="9" t="s">
+      <c r="C456" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -5365,14 +5350,14 @@
         <v>18</v>
       </c>
       <c r="C460" s="8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="461" ht="12.0" customHeight="1">
       <c r="B461" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C461" s="10">
+      <c r="C461" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -5397,7 +5382,7 @@
         <v>36</v>
       </c>
       <c r="C464" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="465" ht="12.0" customHeight="1">
@@ -5411,14 +5396,14 @@
     <row r="466" ht="12.0" customHeight="1"/>
     <row r="467" ht="12.0" customHeight="1">
       <c r="A467" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="468" ht="12.0" customHeight="1">
       <c r="B468" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C468" s="9" t="s">
+      <c r="C468" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -5448,14 +5433,14 @@
         <v>18</v>
       </c>
       <c r="C472" s="8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="473" ht="12.0" customHeight="1">
       <c r="B473" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C473" s="10">
+      <c r="C473" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -5480,7 +5465,7 @@
         <v>36</v>
       </c>
       <c r="C476" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="477" ht="12.0" customHeight="1">
@@ -5493,15 +5478,15 @@
     </row>
     <row r="478" ht="12.0" customHeight="1"/>
     <row r="479" ht="12.0" customHeight="1">
-      <c r="A479" s="9" t="s">
-        <v>121</v>
+      <c r="A479" s="8" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="480" ht="12.0" customHeight="1">
       <c r="B480" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C480" s="9" t="s">
+      <c r="C480" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -5531,14 +5516,14 @@
         <v>18</v>
       </c>
       <c r="C484" s="8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="485" ht="12.0" customHeight="1">
       <c r="B485" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C485" s="10">
+      <c r="C485" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -5563,7 +5548,7 @@
         <v>36</v>
       </c>
       <c r="C488" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="489" ht="12.0" customHeight="1">
@@ -5576,15 +5561,15 @@
     </row>
     <row r="490" ht="12.0" customHeight="1"/>
     <row r="491" ht="12.0" customHeight="1">
-      <c r="A491" s="9" t="s">
-        <v>123</v>
+      <c r="A491" s="8" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="492" ht="12.0" customHeight="1">
       <c r="B492" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C492" s="9" t="s">
+      <c r="C492" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -5614,14 +5599,14 @@
         <v>18</v>
       </c>
       <c r="C496" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="497" ht="12.0" customHeight="1">
       <c r="B497" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C497" s="10">
+      <c r="C497" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -5646,7 +5631,7 @@
         <v>36</v>
       </c>
       <c r="C500" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="501" ht="12.0" customHeight="1">
@@ -5659,15 +5644,15 @@
     </row>
     <row r="502" ht="12.0" customHeight="1"/>
     <row r="503" ht="12.0" customHeight="1">
-      <c r="A503" s="9" t="s">
-        <v>125</v>
+      <c r="A503" s="8" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="504" ht="12.0" customHeight="1">
       <c r="B504" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C504" s="9" t="s">
+      <c r="C504" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -5697,14 +5682,14 @@
         <v>18</v>
       </c>
       <c r="C508" s="8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="509" ht="12.0" customHeight="1">
       <c r="B509" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C509" s="10">
+      <c r="C509" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -5729,7 +5714,7 @@
         <v>36</v>
       </c>
       <c r="C512" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="513" ht="12.0" customHeight="1">
@@ -5743,14 +5728,14 @@
     <row r="514" ht="12.0" customHeight="1"/>
     <row r="515" ht="12.0" customHeight="1">
       <c r="A515" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="516" ht="12.0" customHeight="1">
       <c r="B516" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C516" s="9" t="s">
+      <c r="C516" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -5767,7 +5752,7 @@
         <v>2</v>
       </c>
       <c r="C518" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="519" ht="12.0" customHeight="1">
@@ -5780,14 +5765,14 @@
         <v>18</v>
       </c>
       <c r="C520" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="521" ht="12.0" customHeight="1">
       <c r="B521" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C521" s="10">
+      <c r="C521" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -5826,14 +5811,14 @@
     <row r="526" ht="12.0" customHeight="1"/>
     <row r="527" ht="12.0" customHeight="1">
       <c r="A527" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="528" ht="12.0" customHeight="1">
       <c r="B528" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C528" s="9" t="s">
+      <c r="C528" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -5850,7 +5835,7 @@
         <v>2</v>
       </c>
       <c r="C530" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="531" ht="12.0" customHeight="1">
@@ -5863,14 +5848,14 @@
         <v>18</v>
       </c>
       <c r="C532" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="533" ht="12.0" customHeight="1">
       <c r="B533" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C533" s="10">
+      <c r="C533" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -5909,14 +5894,14 @@
     <row r="538" ht="12.0" customHeight="1"/>
     <row r="539" ht="12.0" customHeight="1">
       <c r="A539" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="540" ht="12.0" customHeight="1">
       <c r="B540" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C540" s="9" t="s">
+      <c r="C540" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -5933,7 +5918,7 @@
         <v>2</v>
       </c>
       <c r="C542" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="543" ht="12.0" customHeight="1">
@@ -5946,14 +5931,14 @@
         <v>18</v>
       </c>
       <c r="C544" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="545" ht="12.0" customHeight="1">
       <c r="B545" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C545" s="10">
+      <c r="C545" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -5992,14 +5977,14 @@
     <row r="550" ht="12.0" customHeight="1"/>
     <row r="551" ht="12.0" customHeight="1">
       <c r="A551" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="552" ht="12.0" customHeight="1">
       <c r="B552" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C552" s="9" t="s">
+      <c r="C552" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -6029,14 +6014,14 @@
         <v>18</v>
       </c>
       <c r="C556" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="557" ht="12.0" customHeight="1">
       <c r="B557" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C557" s="10">
+      <c r="C557" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -6075,14 +6060,14 @@
     <row r="562" ht="12.0" customHeight="1"/>
     <row r="563" ht="12.0" customHeight="1">
       <c r="A563" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="564" ht="12.0" customHeight="1">
       <c r="B564" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C564" s="9" t="s">
+      <c r="C564" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -6112,14 +6097,14 @@
         <v>18</v>
       </c>
       <c r="C568" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="569" ht="12.0" customHeight="1">
       <c r="B569" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C569" s="10">
+      <c r="C569" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -6158,14 +6143,14 @@
     <row r="574" ht="12.0" customHeight="1"/>
     <row r="575" ht="12.0" customHeight="1">
       <c r="A575" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="576" ht="12.0" customHeight="1">
       <c r="B576" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C576" s="9" t="s">
+      <c r="C576" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -6195,14 +6180,14 @@
         <v>18</v>
       </c>
       <c r="C580" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="581" ht="12.0" customHeight="1">
       <c r="B581" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C581" s="10">
+      <c r="C581" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -6240,15 +6225,15 @@
     </row>
     <row r="586" ht="12.0" customHeight="1"/>
     <row r="587" ht="12.0" customHeight="1">
-      <c r="A587" s="9" t="s">
-        <v>139</v>
+      <c r="A587" s="8" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="588" ht="12.0" customHeight="1">
       <c r="B588" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C588" s="9" t="s">
+      <c r="C588" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -6278,14 +6263,14 @@
         <v>18</v>
       </c>
       <c r="C592" s="8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="593" ht="12.0" customHeight="1">
       <c r="B593" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C593" s="10">
+      <c r="C593" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -6323,15 +6308,15 @@
     </row>
     <row r="598" ht="12.0" customHeight="1"/>
     <row r="599" ht="12.0" customHeight="1">
-      <c r="A599" s="9" t="s">
-        <v>141</v>
+      <c r="A599" s="8" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="600" ht="12.0" customHeight="1">
       <c r="B600" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C600" s="9" t="s">
+      <c r="C600" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -6361,14 +6346,14 @@
         <v>18</v>
       </c>
       <c r="C604" s="8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="605" ht="12.0" customHeight="1">
       <c r="B605" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C605" s="10">
+      <c r="C605" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -6406,15 +6391,15 @@
     </row>
     <row r="610" ht="12.0" customHeight="1"/>
     <row r="611" ht="12.0" customHeight="1">
-      <c r="A611" s="9" t="s">
-        <v>143</v>
+      <c r="A611" s="8" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="612" ht="12.0" customHeight="1">
       <c r="B612" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C612" s="9" t="s">
+      <c r="C612" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -6444,14 +6429,14 @@
         <v>18</v>
       </c>
       <c r="C616" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="617" ht="12.0" customHeight="1">
       <c r="B617" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C617" s="10">
+      <c r="C617" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -6490,14 +6475,14 @@
     <row r="622" ht="12.0" customHeight="1"/>
     <row r="623" ht="12.0" customHeight="1">
       <c r="A623" s="8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="624" ht="12.0" customHeight="1">
       <c r="B624" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C624" s="9" t="s">
+      <c r="C624" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -6514,7 +6499,7 @@
         <v>2</v>
       </c>
       <c r="C626" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="627" ht="12.0" customHeight="1">
@@ -6527,14 +6512,14 @@
         <v>18</v>
       </c>
       <c r="C628" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="629" ht="12.0" customHeight="1">
       <c r="B629" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C629" s="10">
+      <c r="C629" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -6573,14 +6558,14 @@
     <row r="634" ht="12.0" customHeight="1"/>
     <row r="635" ht="12.0" customHeight="1">
       <c r="A635" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="636" ht="12.0" customHeight="1">
       <c r="B636" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C636" s="9" t="s">
+      <c r="C636" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -6597,7 +6582,7 @@
         <v>2</v>
       </c>
       <c r="C638" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="639" ht="12.0" customHeight="1">
@@ -6610,14 +6595,14 @@
         <v>18</v>
       </c>
       <c r="C640" s="8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="641" ht="12.0" customHeight="1">
       <c r="B641" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C641" s="10">
+      <c r="C641" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -6656,14 +6641,14 @@
     <row r="646" ht="12.0" customHeight="1"/>
     <row r="647" ht="12.0" customHeight="1">
       <c r="A647" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="648" ht="12.0" customHeight="1">
       <c r="B648" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C648" s="9" t="s">
+      <c r="C648" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -6680,7 +6665,7 @@
         <v>2</v>
       </c>
       <c r="C650" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="651" ht="12.0" customHeight="1">
@@ -6693,14 +6678,14 @@
         <v>18</v>
       </c>
       <c r="C652" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="653" ht="12.0" customHeight="1">
       <c r="B653" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C653" s="10">
+      <c r="C653" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -6739,14 +6724,14 @@
     <row r="658" ht="12.0" customHeight="1"/>
     <row r="659" ht="12.0" customHeight="1">
       <c r="A659" s="8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="660" ht="12.0" customHeight="1">
       <c r="B660" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C660" s="9" t="s">
+      <c r="C660" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -6763,7 +6748,7 @@
         <v>2</v>
       </c>
       <c r="C662" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="663" ht="12.0" customHeight="1">
@@ -6776,14 +6761,14 @@
         <v>18</v>
       </c>
       <c r="C664" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="665" ht="12.0" customHeight="1">
       <c r="B665" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C665" s="10">
+      <c r="C665" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -6822,14 +6807,14 @@
     <row r="670" ht="12.0" customHeight="1"/>
     <row r="671" ht="12.0" customHeight="1">
       <c r="A671" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="672" ht="12.0" customHeight="1">
       <c r="B672" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C672" s="9" t="s">
+      <c r="C672" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -6846,7 +6831,7 @@
         <v>2</v>
       </c>
       <c r="C674" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="675" ht="12.0" customHeight="1">
@@ -6859,14 +6844,14 @@
         <v>18</v>
       </c>
       <c r="C676" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="677" ht="12.0" customHeight="1">
       <c r="B677" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C677" s="10">
+      <c r="C677" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -6905,14 +6890,14 @@
     <row r="682" ht="12.0" customHeight="1"/>
     <row r="683" ht="12.0" customHeight="1">
       <c r="A683" s="8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="684" ht="12.0" customHeight="1">
       <c r="B684" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C684" s="9" t="s">
+      <c r="C684" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -6929,7 +6914,7 @@
         <v>2</v>
       </c>
       <c r="C686" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="687" ht="12.0" customHeight="1">
@@ -6942,14 +6927,14 @@
         <v>18</v>
       </c>
       <c r="C688" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="689" ht="12.0" customHeight="1">
       <c r="B689" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C689" s="10">
+      <c r="C689" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -6988,14 +6973,14 @@
     <row r="694" ht="12.0" customHeight="1"/>
     <row r="695" ht="12.0" customHeight="1">
       <c r="A695" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="696" ht="12.0" customHeight="1">
       <c r="B696" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C696" s="9" t="s">
+      <c r="C696" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -7012,7 +6997,7 @@
         <v>2</v>
       </c>
       <c r="C698" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="699" ht="12.0" customHeight="1">
@@ -7025,14 +7010,14 @@
         <v>18</v>
       </c>
       <c r="C700" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="701" ht="12.0" customHeight="1">
       <c r="B701" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C701" s="10">
+      <c r="C701" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -7071,14 +7056,14 @@
     <row r="706" ht="12.0" customHeight="1"/>
     <row r="707" ht="12.0" customHeight="1">
       <c r="A707" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="708" ht="12.0" customHeight="1">
       <c r="B708" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C708" s="9" t="s">
+      <c r="C708" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -7095,7 +7080,7 @@
         <v>2</v>
       </c>
       <c r="C710" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="711" ht="12.0" customHeight="1">
@@ -7108,14 +7093,14 @@
         <v>18</v>
       </c>
       <c r="C712" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="713" ht="12.0" customHeight="1">
       <c r="B713" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C713" s="10">
+      <c r="C713" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -7153,15 +7138,15 @@
     </row>
     <row r="718" ht="12.0" customHeight="1"/>
     <row r="719" ht="12.0" customHeight="1">
-      <c r="A719" s="9" t="s">
-        <v>164</v>
+      <c r="A719" s="8" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="720" ht="12.0" customHeight="1">
       <c r="B720" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C720" s="9" t="s">
+      <c r="C720" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -7178,7 +7163,7 @@
         <v>2</v>
       </c>
       <c r="C722" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="723" ht="12.0" customHeight="1">
@@ -7191,14 +7176,14 @@
         <v>18</v>
       </c>
       <c r="C724" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="725" ht="12.0" customHeight="1">
       <c r="B725" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C725" s="10">
+      <c r="C725" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -7237,14 +7222,14 @@
     <row r="730" ht="12.0" customHeight="1"/>
     <row r="731" ht="12.0" customHeight="1">
       <c r="A731" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="732" ht="12.0" customHeight="1">
       <c r="B732" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C732" s="9" t="s">
+      <c r="C732" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -7261,7 +7246,7 @@
         <v>2</v>
       </c>
       <c r="C734" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="735" ht="12.0" customHeight="1">
@@ -7274,14 +7259,14 @@
         <v>18</v>
       </c>
       <c r="C736" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="737" ht="12.0" customHeight="1">
       <c r="B737" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C737" s="10">
+      <c r="C737" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -7319,15 +7304,15 @@
     </row>
     <row r="742" ht="12.0" customHeight="1"/>
     <row r="743" ht="12.0" customHeight="1">
-      <c r="A743" s="9" t="s">
-        <v>169</v>
+      <c r="A743" s="8" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="744" ht="12.0" customHeight="1">
       <c r="B744" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C744" s="9" t="s">
+      <c r="C744" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -7344,7 +7329,7 @@
         <v>2</v>
       </c>
       <c r="C746" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="747" ht="12.0" customHeight="1">
@@ -7357,14 +7342,14 @@
         <v>18</v>
       </c>
       <c r="C748" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="749" ht="12.0" customHeight="1">
       <c r="B749" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C749" s="10">
+      <c r="C749" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -7403,14 +7388,14 @@
     <row r="754" ht="12.0" customHeight="1"/>
     <row r="755" ht="12.0" customHeight="1">
       <c r="A755" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="756" ht="12.0" customHeight="1">
       <c r="B756" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C756" s="9" t="s">
+      <c r="C756" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -7427,7 +7412,7 @@
         <v>2</v>
       </c>
       <c r="C758" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="759" ht="12.0" customHeight="1">
@@ -7440,14 +7425,14 @@
         <v>18</v>
       </c>
       <c r="C760" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="761" ht="12.0" customHeight="1">
       <c r="B761" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C761" s="10">
+      <c r="C761" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -7472,7 +7457,7 @@
         <v>36</v>
       </c>
       <c r="C764" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="765" ht="12.0" customHeight="1">
@@ -7486,14 +7471,14 @@
     <row r="766" ht="12.0" customHeight="1"/>
     <row r="767" ht="12.0" customHeight="1">
       <c r="A767" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="768" ht="12.0" customHeight="1">
       <c r="B768" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C768" s="9" t="s">
+      <c r="C768" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -7510,7 +7495,7 @@
         <v>2</v>
       </c>
       <c r="C770" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="771" ht="12.0" customHeight="1">
@@ -7523,14 +7508,14 @@
         <v>18</v>
       </c>
       <c r="C772" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="773" ht="12.0" customHeight="1">
       <c r="B773" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C773" s="10">
+      <c r="C773" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -7555,7 +7540,7 @@
         <v>36</v>
       </c>
       <c r="C776" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="777" ht="12.0" customHeight="1">
@@ -7569,14 +7554,14 @@
     <row r="778" ht="12.0" customHeight="1"/>
     <row r="779" ht="12.0" customHeight="1">
       <c r="A779" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="780" ht="12.0" customHeight="1">
       <c r="B780" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C780" s="9" t="s">
+      <c r="C780" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -7593,7 +7578,7 @@
         <v>2</v>
       </c>
       <c r="C782" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="783" ht="12.0" customHeight="1">
@@ -7606,14 +7591,14 @@
         <v>18</v>
       </c>
       <c r="C784" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="785" ht="12.0" customHeight="1">
       <c r="B785" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C785" s="10">
+      <c r="C785" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -7638,7 +7623,7 @@
         <v>36</v>
       </c>
       <c r="C788" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="789" ht="12.0" customHeight="1">
@@ -7652,14 +7637,14 @@
     <row r="790" ht="12.0" customHeight="1"/>
     <row r="791" ht="12.0" customHeight="1">
       <c r="A791" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="792" ht="12.0" customHeight="1">
       <c r="B792" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C792" s="9" t="s">
+      <c r="C792" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -7676,7 +7661,7 @@
         <v>2</v>
       </c>
       <c r="C794" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="795" ht="12.0" customHeight="1">
@@ -7689,14 +7674,14 @@
         <v>18</v>
       </c>
       <c r="C796" s="8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="797" ht="12.0" customHeight="1">
       <c r="B797" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C797" s="10">
+      <c r="C797" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -7721,7 +7706,7 @@
         <v>36</v>
       </c>
       <c r="C800" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="801" ht="12.0" customHeight="1">
@@ -7735,14 +7720,14 @@
     <row r="802" ht="12.0" customHeight="1"/>
     <row r="803" ht="12.0" customHeight="1">
       <c r="A803" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="804" ht="12.0" customHeight="1">
       <c r="B804" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C804" s="9" t="s">
+      <c r="C804" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -7759,7 +7744,7 @@
         <v>2</v>
       </c>
       <c r="C806" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="807" ht="12.0" customHeight="1">
@@ -7772,14 +7757,14 @@
         <v>18</v>
       </c>
       <c r="C808" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="809" ht="12.0" customHeight="1">
       <c r="B809" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C809" s="10">
+      <c r="C809" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -7804,7 +7789,7 @@
         <v>36</v>
       </c>
       <c r="C812" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="813" ht="12.0" customHeight="1">
@@ -7818,14 +7803,14 @@
     <row r="814" ht="12.0" customHeight="1"/>
     <row r="815" ht="12.0" customHeight="1">
       <c r="A815" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="816" ht="12.0" customHeight="1">
       <c r="B816" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C816" s="9" t="s">
+      <c r="C816" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -7842,7 +7827,7 @@
         <v>2</v>
       </c>
       <c r="C818" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="819" ht="12.0" customHeight="1">
@@ -7855,14 +7840,14 @@
         <v>18</v>
       </c>
       <c r="C820" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="821" ht="12.0" customHeight="1">
       <c r="B821" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C821" s="10">
+      <c r="C821" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -7887,7 +7872,7 @@
         <v>36</v>
       </c>
       <c r="C824" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="825" ht="12.0" customHeight="1">
@@ -7901,14 +7886,14 @@
     <row r="826" ht="12.0" customHeight="1"/>
     <row r="827" ht="12.0" customHeight="1">
       <c r="A827" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="828" ht="12.0" customHeight="1">
       <c r="B828" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C828" s="9" t="s">
+      <c r="C828" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -7925,7 +7910,7 @@
         <v>2</v>
       </c>
       <c r="C830" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="831" ht="12.0" customHeight="1">
@@ -7938,14 +7923,14 @@
         <v>18</v>
       </c>
       <c r="C832" s="8" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="833" ht="12.0" customHeight="1">
       <c r="B833" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C833" s="10">
+      <c r="C833" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -7970,7 +7955,7 @@
         <v>36</v>
       </c>
       <c r="C836" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="837" ht="12.0" customHeight="1">
@@ -7984,14 +7969,14 @@
     <row r="838" ht="12.0" customHeight="1"/>
     <row r="839" ht="12.0" customHeight="1">
       <c r="A839" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="840" ht="12.0" customHeight="1">
       <c r="B840" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C840" s="9" t="s">
+      <c r="C840" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -8008,7 +7993,7 @@
         <v>2</v>
       </c>
       <c r="C842" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="843" ht="12.0" customHeight="1">
@@ -8021,14 +8006,14 @@
         <v>18</v>
       </c>
       <c r="C844" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="845" ht="12.0" customHeight="1">
       <c r="B845" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C845" s="10">
+      <c r="C845" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -8053,7 +8038,7 @@
         <v>36</v>
       </c>
       <c r="C848" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="849" ht="12.0" customHeight="1">
@@ -8066,15 +8051,15 @@
     </row>
     <row r="850" ht="12.0" customHeight="1"/>
     <row r="851" ht="12.0" customHeight="1">
-      <c r="A851" s="9" t="s">
-        <v>187</v>
+      <c r="A851" s="8" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="852" ht="12.0" customHeight="1">
       <c r="B852" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C852" s="9" t="s">
+      <c r="C852" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -8091,7 +8076,7 @@
         <v>2</v>
       </c>
       <c r="C854" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="855" ht="12.0" customHeight="1">
@@ -8104,14 +8089,14 @@
         <v>18</v>
       </c>
       <c r="C856" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="857" ht="12.0" customHeight="1">
       <c r="B857" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C857" s="10">
+      <c r="C857" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -8136,7 +8121,7 @@
         <v>36</v>
       </c>
       <c r="C860" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="861" ht="12.0" customHeight="1">
@@ -8149,15 +8134,15 @@
     </row>
     <row r="862" ht="12.0" customHeight="1"/>
     <row r="863" ht="12.0" customHeight="1">
-      <c r="A863" s="9" t="s">
-        <v>189</v>
+      <c r="A863" s="8" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="864" ht="12.0" customHeight="1">
       <c r="B864" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C864" s="9" t="s">
+      <c r="C864" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -8174,7 +8159,7 @@
         <v>2</v>
       </c>
       <c r="C866" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="867" ht="12.0" customHeight="1">
@@ -8187,14 +8172,14 @@
         <v>18</v>
       </c>
       <c r="C868" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="869" ht="12.0" customHeight="1">
       <c r="B869" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C869" s="10">
+      <c r="C869" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -8219,7 +8204,7 @@
         <v>36</v>
       </c>
       <c r="C872" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="873" ht="12.0" customHeight="1">
@@ -8232,15 +8217,15 @@
     </row>
     <row r="874" ht="12.0" customHeight="1"/>
     <row r="875" ht="12.0" customHeight="1">
-      <c r="A875" s="9" t="s">
-        <v>191</v>
+      <c r="A875" s="8" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="876" ht="12.0" customHeight="1">
       <c r="B876" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C876" s="9" t="s">
+      <c r="C876" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -8257,7 +8242,7 @@
         <v>2</v>
       </c>
       <c r="C878" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="879" ht="12.0" customHeight="1">
@@ -8270,14 +8255,14 @@
         <v>18</v>
       </c>
       <c r="C880" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="881" ht="12.0" customHeight="1">
       <c r="B881" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C881" s="10">
+      <c r="C881" s="9">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -8302,7 +8287,7 @@
         <v>36</v>
       </c>
       <c r="C884" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="885" ht="12.0" customHeight="1">
@@ -8316,15 +8301,15 @@
     <row r="886" ht="12.0" customHeight="1"/>
     <row r="887" ht="12.0" customHeight="1">
       <c r="A887" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="888" ht="12.0" customHeight="1">
       <c r="B888" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C888" s="9" t="s">
-        <v>194</v>
+      <c r="C888" s="8" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="889" ht="12.0" customHeight="1">
@@ -8353,38 +8338,38 @@
         <v>18</v>
       </c>
       <c r="C892" s="8" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="893" ht="12.0" customHeight="1">
+      <c r="B893" s="12" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="893" ht="12.0" customHeight="1">
-      <c r="B893" s="13" t="s">
+      <c r="C893" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="C893" s="14" t="s">
+    </row>
+    <row r="894" ht="15.75" customHeight="1">
+      <c r="A894" s="13"/>
+      <c r="B894" s="14" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="894">
-      <c r="A894" s="15"/>
-      <c r="B894" s="16" t="s">
+      <c r="C894" s="14" t="s">
         <v>198</v>
-      </c>
-      <c r="C894" s="17" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="895" ht="12.0" customHeight="1"/>
     <row r="896" ht="12.0" customHeight="1">
       <c r="A896" s="8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="897" ht="12.0" customHeight="1">
       <c r="B897" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C897" s="9" t="s">
-        <v>194</v>
+      <c r="C897" s="8" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="898" ht="12.0" customHeight="1">
@@ -8413,37 +8398,37 @@
         <v>18</v>
       </c>
       <c r="C901" s="8" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="902" ht="12.0" customHeight="1">
-      <c r="B902" s="13" t="s">
+      <c r="B902" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="C902" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="C902" s="14" t="s">
+    </row>
+    <row r="903" ht="15.75" customHeight="1">
+      <c r="B903" s="14" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="903">
-      <c r="B903" s="16" t="s">
+      <c r="C903" s="14" t="s">
         <v>198</v>
-      </c>
-      <c r="C903" s="17" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="904" ht="12.0" customHeight="1"/>
     <row r="905" ht="12.0" customHeight="1">
       <c r="A905" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="906" ht="12.0" customHeight="1">
       <c r="B906" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C906" s="9" t="s">
-        <v>194</v>
+      <c r="C906" s="8" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="907" ht="12.0" customHeight="1">
@@ -8472,37 +8457,37 @@
         <v>18</v>
       </c>
       <c r="C910" s="8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="911" ht="12.0" customHeight="1">
-      <c r="B911" s="13" t="s">
+      <c r="B911" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="C911" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="C911" s="14" t="s">
+    </row>
+    <row r="912" ht="15.75" customHeight="1">
+      <c r="B912" s="14" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="912">
-      <c r="B912" s="16" t="s">
+      <c r="C912" s="14" t="s">
         <v>198</v>
-      </c>
-      <c r="C912" s="17" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="913" ht="12.0" customHeight="1"/>
     <row r="914" ht="12.0" customHeight="1">
       <c r="A914" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="915" ht="12.0" customHeight="1">
       <c r="B915" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C915" s="9" t="s">
-        <v>194</v>
+      <c r="C915" s="8" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="916" ht="12.0" customHeight="1">
@@ -8531,37 +8516,37 @@
         <v>18</v>
       </c>
       <c r="C919" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="920" ht="12.0" customHeight="1">
-      <c r="B920" s="13" t="s">
+      <c r="B920" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="C920" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="C920" s="14" t="s">
+    </row>
+    <row r="921" ht="15.75" customHeight="1">
+      <c r="B921" s="14" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="921">
-      <c r="B921" s="16" t="s">
+      <c r="C921" s="14" t="s">
         <v>198</v>
-      </c>
-      <c r="C921" s="17" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="922" ht="12.0" customHeight="1"/>
     <row r="923" ht="12.0" customHeight="1">
       <c r="A923" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="924" ht="12.0" customHeight="1">
       <c r="B924" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C924" s="9" t="s">
-        <v>194</v>
+      <c r="C924" s="8" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="925" ht="12.0" customHeight="1">
@@ -8590,37 +8575,37 @@
         <v>18</v>
       </c>
       <c r="C928" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="929" ht="12.0" customHeight="1">
-      <c r="B929" s="13" t="s">
+      <c r="B929" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="C929" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="C929" s="14" t="s">
+    </row>
+    <row r="930" ht="15.75" customHeight="1">
+      <c r="B930" s="14" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="930">
-      <c r="B930" s="16" t="s">
+      <c r="C930" s="14" t="s">
         <v>198</v>
-      </c>
-      <c r="C930" s="17" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="931" ht="12.0" customHeight="1"/>
     <row r="932" ht="12.0" customHeight="1">
       <c r="A932" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="933" ht="12.0" customHeight="1">
       <c r="B933" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C933" s="9" t="s">
-        <v>194</v>
+      <c r="C933" s="8" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="934" ht="12.0" customHeight="1">
@@ -8649,37 +8634,37 @@
         <v>18</v>
       </c>
       <c r="C937" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="938" ht="12.0" customHeight="1">
-      <c r="B938" s="13" t="s">
+      <c r="B938" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="C938" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="C938" s="14" t="s">
+    </row>
+    <row r="939" ht="15.75" customHeight="1">
+      <c r="B939" s="14" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="939">
-      <c r="B939" s="16" t="s">
+      <c r="C939" s="14" t="s">
         <v>198</v>
-      </c>
-      <c r="C939" s="17" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="940" ht="12.0" customHeight="1"/>
     <row r="941" ht="12.0" customHeight="1">
       <c r="A941" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="942" ht="12.0" customHeight="1">
       <c r="B942" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C942" s="9" t="s">
-        <v>194</v>
+      <c r="C942" s="8" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="943" ht="12.0" customHeight="1">
@@ -8708,37 +8693,37 @@
         <v>18</v>
       </c>
       <c r="C946" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="947" ht="12.0" customHeight="1">
-      <c r="B947" s="13" t="s">
+      <c r="B947" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="C947" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="C947" s="14" t="s">
+    </row>
+    <row r="948" ht="15.75" customHeight="1">
+      <c r="B948" s="14" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="948">
-      <c r="B948" s="16" t="s">
+      <c r="C948" s="14" t="s">
         <v>198</v>
-      </c>
-      <c r="C948" s="17" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="949" ht="12.0" customHeight="1"/>
     <row r="950" ht="12.0" customHeight="1">
       <c r="A950" s="8" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="951" ht="12.0" customHeight="1">
       <c r="B951" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C951" s="9" t="s">
-        <v>194</v>
+      <c r="C951" s="8" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="952" ht="12.0" customHeight="1">
@@ -8767,37 +8752,37 @@
         <v>18</v>
       </c>
       <c r="C955" s="8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="956" ht="12.0" customHeight="1">
-      <c r="B956" s="13" t="s">
+      <c r="B956" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="C956" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="C956" s="14" t="s">
+    </row>
+    <row r="957" ht="15.75" customHeight="1">
+      <c r="B957" s="14" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="957">
-      <c r="B957" s="16" t="s">
+      <c r="C957" s="14" t="s">
         <v>198</v>
-      </c>
-      <c r="C957" s="17" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="958" ht="12.0" customHeight="1"/>
     <row r="959" ht="12.0" customHeight="1">
       <c r="A959" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="960" ht="12.0" customHeight="1">
       <c r="B960" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C960" s="9" t="s">
-        <v>194</v>
+      <c r="C960" s="8" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="961" ht="12.0" customHeight="1">
@@ -8826,37 +8811,37 @@
         <v>18</v>
       </c>
       <c r="C964" s="8" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="965" ht="12.0" customHeight="1">
+      <c r="B965" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="C965" s="11" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="965" ht="12.0" customHeight="1">
-      <c r="B965" s="13" t="s">
-        <v>196</v>
-      </c>
-      <c r="C965" s="11" t="s">
+    <row r="966" ht="15.75" customHeight="1">
+      <c r="B966" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="C966" s="14" t="s">
         <v>216</v>
-      </c>
-    </row>
-    <row r="966">
-      <c r="B966" s="16" t="s">
-        <v>198</v>
-      </c>
-      <c r="C966" s="16" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="967" ht="12.0" customHeight="1"/>
     <row r="968" ht="12.0" customHeight="1">
       <c r="A968" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="969" ht="12.0" customHeight="1">
       <c r="B969" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C969" s="9" t="s">
-        <v>194</v>
+      <c r="C969" s="8" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="970" ht="12.0" customHeight="1">
@@ -8885,37 +8870,37 @@
         <v>18</v>
       </c>
       <c r="C973" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="974" ht="12.0" customHeight="1">
-      <c r="B974" s="13" t="s">
-        <v>196</v>
+      <c r="B974" s="12" t="s">
+        <v>195</v>
       </c>
       <c r="C974" s="11" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="975" ht="15.75" customHeight="1">
+      <c r="B975" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="C975" s="14" t="s">
         <v>216</v>
-      </c>
-    </row>
-    <row r="975">
-      <c r="B975" s="16" t="s">
-        <v>198</v>
-      </c>
-      <c r="C975" s="16" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="976" ht="12.0" customHeight="1"/>
     <row r="977" ht="12.0" customHeight="1">
       <c r="A977" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="978" ht="12.0" customHeight="1">
       <c r="B978" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C978" s="9" t="s">
-        <v>194</v>
+      <c r="C978" s="8" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="979" ht="12.0" customHeight="1">
@@ -8944,37 +8929,37 @@
         <v>18</v>
       </c>
       <c r="C982" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="983" ht="12.0" customHeight="1">
-      <c r="B983" s="13" t="s">
-        <v>196</v>
+      <c r="B983" s="12" t="s">
+        <v>195</v>
       </c>
       <c r="C983" s="11" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="984" ht="15.75" customHeight="1">
+      <c r="B984" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="C984" s="14" t="s">
         <v>216</v>
-      </c>
-    </row>
-    <row r="984">
-      <c r="B984" s="16" t="s">
-        <v>198</v>
-      </c>
-      <c r="C984" s="16" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="985" ht="12.0" customHeight="1"/>
     <row r="986" ht="12.0" customHeight="1">
       <c r="A986" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="987" ht="12.0" customHeight="1">
       <c r="B987" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C987" s="9" t="s">
-        <v>194</v>
+      <c r="C987" s="8" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="988" ht="12.0" customHeight="1">
@@ -9003,37 +8988,37 @@
         <v>18</v>
       </c>
       <c r="C991" s="8" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="992" ht="12.0" customHeight="1">
+      <c r="B992" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="C992" s="11" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="992" ht="12.0" customHeight="1">
-      <c r="B992" s="13" t="s">
-        <v>196</v>
-      </c>
-      <c r="C992" s="14" t="s">
+    <row r="993" ht="15.75" customHeight="1">
+      <c r="B993" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="C993" s="14" t="s">
         <v>224</v>
-      </c>
-    </row>
-    <row r="993">
-      <c r="B993" s="16" t="s">
-        <v>198</v>
-      </c>
-      <c r="C993" s="17" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="994" ht="12.0" customHeight="1"/>
     <row r="995" ht="12.0" customHeight="1">
       <c r="A995" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="996" ht="12.0" customHeight="1">
       <c r="B996" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C996" s="9" t="s">
-        <v>194</v>
+      <c r="C996" s="8" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="997" ht="12.0" customHeight="1">
@@ -9062,37 +9047,37 @@
         <v>18</v>
       </c>
       <c r="C1000" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="1001" ht="12.0" customHeight="1">
-      <c r="B1001" s="13" t="s">
-        <v>196</v>
-      </c>
-      <c r="C1001" s="14" t="s">
+      <c r="B1001" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="C1001" s="11" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="1002" ht="15.75" customHeight="1">
+      <c r="B1002" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="C1002" s="14" t="s">
         <v>224</v>
-      </c>
-    </row>
-    <row r="1002">
-      <c r="B1002" s="16" t="s">
-        <v>198</v>
-      </c>
-      <c r="C1002" s="17" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="1003" ht="12.0" customHeight="1"/>
     <row r="1004" ht="12.0" customHeight="1">
       <c r="A1004" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="1005" ht="12.0" customHeight="1">
       <c r="B1005" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C1005" s="9" t="s">
-        <v>194</v>
+      <c r="C1005" s="8" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="1006" ht="12.0" customHeight="1">
@@ -9121,37 +9106,37 @@
         <v>18</v>
       </c>
       <c r="C1009" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="1010" ht="12.0" customHeight="1">
-      <c r="B1010" s="13" t="s">
-        <v>196</v>
-      </c>
-      <c r="C1010" s="14" t="s">
+      <c r="B1010" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="C1010" s="11" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="1011" ht="15.75" customHeight="1">
+      <c r="B1011" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="C1011" s="14" t="s">
         <v>224</v>
-      </c>
-    </row>
-    <row r="1011">
-      <c r="B1011" s="16" t="s">
-        <v>198</v>
-      </c>
-      <c r="C1011" s="17" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="1012" ht="12.0" customHeight="1"/>
     <row r="1013" ht="12.0" customHeight="1">
       <c r="A1013" s="8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="1014" ht="12.0" customHeight="1">
       <c r="B1014" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C1014" s="9" t="s">
-        <v>194</v>
+      <c r="C1014" s="8" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="1015" ht="12.0" customHeight="1">
@@ -9179,24 +9164,24 @@
       <c r="B1018" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C1018" s="9" t="s">
-        <v>231</v>
+      <c r="C1018" s="8" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="1019" ht="12.0" customHeight="1">
-      <c r="B1019" s="13" t="s">
-        <v>196</v>
-      </c>
-      <c r="C1019" s="14" t="s">
+      <c r="B1019" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="C1019" s="11" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="1020" ht="15.75" customHeight="1">
+      <c r="B1020" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="C1020" s="14" t="s">
         <v>224</v>
-      </c>
-    </row>
-    <row r="1020">
-      <c r="B1020" s="16" t="s">
-        <v>198</v>
-      </c>
-      <c r="C1020" s="17" t="s">
-        <v>225</v>
       </c>
     </row>
   </sheetData>
